--- a/mds-agents/agents/now_analyzer/tools/now_regional_checklist.xlsx
+++ b/mds-agents/agents/now_analyzer/tools/now_regional_checklist.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcgov-my.sharepoint.com/personal/rebecca_stevenson_gov_bc_ca/Documents/Application Intake/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mines Operations\Smithers\PERMITTING\!Core Transition\!NOW-files in process\0200216_Topley Richfield\0200216-2026-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B554CC26-C34B-4DB5-950C-9256B6D47445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3370D4A-BAA0-4E8E-9A99-4055177DBB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="420" windowWidth="25440" windowHeight="15270" xr2:uid="{00628202-5D29-4ABA-801F-5A4DBCDE3563}"/>
+    <workbookView xWindow="-30828" yWindow="-1248" windowWidth="30936" windowHeight="16776" xr2:uid="{51877E8C-9182-4181-B63A-3A152A573607}"/>
   </bookViews>
   <sheets>
     <sheet name="MX Intake Checklist" sheetId="1" r:id="rId1"/>
+    <sheet name="Guidance" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="AT">[1]MAA!$F$5:$F$8</definedName>
@@ -46,9 +47,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -56,10 +54,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={202AD996-6DC7-4D61-8C96-0F781393163C}</author>
+    <author>tc={A6ACB50C-203F-45F9-8AD5-76597DDFFB39}</author>
   </authors>
   <commentList>
-    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{202AD996-6DC7-4D61-8C96-0F781393163C}">
+    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{A6ACB50C-203F-45F9-8AD5-76597DDFFB39}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -72,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="351">
   <si>
     <t>Required</t>
   </si>
@@ -86,27 +84,42 @@
     <t>Intake Process</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Create application file in the LAN</t>
+  </si>
+  <si>
+    <t>Download NoW Application and documents and save in the LAN</t>
+  </si>
+  <si>
     <t>Enter NoW information into the 'Line Up' tab of the NoW tracker</t>
   </si>
   <si>
     <t>Fill NoW # cell yellow until pushed to Core</t>
   </si>
   <si>
-    <t>Create application file in the LAN</t>
-  </si>
-  <si>
-    <t>Download NoW Application and documents and save in the LAN</t>
-  </si>
-  <si>
     <t>Review NoW</t>
   </si>
   <si>
     <t>NoW Application Completeness</t>
   </si>
   <si>
+    <t>Pre-status</t>
+  </si>
+  <si>
     <t>Determine MX Tier</t>
   </si>
   <si>
+    <t>Consult Indigenous Relations team (email them the checklist?)</t>
+  </si>
+  <si>
+    <t>Change MX Tier if Indigenous Relations team identifies new tier level</t>
+  </si>
+  <si>
+    <t>Add MX Tier and ensure Deadline date is correct in NoW Tracker</t>
+  </si>
+  <si>
     <t>Change file status on the NoW Tracker to 'GIS Start'</t>
   </si>
   <si>
@@ -119,6 +132,12 @@
     <t>Associate Orgbook if applicable</t>
   </si>
   <si>
+    <t>Go into Administrative section in Core and add the date that it was pushed to Core</t>
+  </si>
+  <si>
+    <t>Fill in the NoW Checklist</t>
+  </si>
+  <si>
     <t>Send Application Accepted/Not-Accepted email to proponent</t>
   </si>
   <si>
@@ -128,18 +147,24 @@
     <t>Project Name:</t>
   </si>
   <si>
-    <t>NoW #:</t>
+    <t>FCBC NoW #:</t>
   </si>
   <si>
     <t>Application Type:</t>
   </si>
   <si>
+    <t>MX Tier #:</t>
+  </si>
+  <si>
     <t>Date Received:</t>
   </si>
   <si>
     <t>Date(s) Sent Back:</t>
   </si>
   <si>
+    <t>Additional Attachments</t>
+  </si>
+  <si>
     <t>Map - Location</t>
   </si>
   <si>
@@ -164,12 +189,18 @@
     <t>Annual Summary (current year/up to date) *Hold up if multiple year reports missing</t>
   </si>
   <si>
+    <t>Wildlife Management Plan (Inspector request)</t>
+  </si>
+  <si>
     <t>Mine Emergency Response Plan (MERP)</t>
   </si>
   <si>
     <t>Erosion and Sediment Control Plan (Inspector request)</t>
   </si>
   <si>
+    <t>Content and Attachments</t>
+  </si>
+  <si>
     <t>Applicant Information</t>
   </si>
   <si>
@@ -194,6 +225,9 @@
     <t>Tenures/Mineral Crown Grant</t>
   </si>
   <si>
+    <t>Tenure #'s</t>
+  </si>
+  <si>
     <t>Ownership Check - (download spreadsheet from MTO)</t>
   </si>
   <si>
@@ -239,12 +273,12 @@
     <t>Cultural Heritage Resources</t>
   </si>
   <si>
-    <t xml:space="preserve">Cultural Heritage Protection Plan </t>
-  </si>
-  <si>
     <t>Archaeological Chance Find Procedure</t>
   </si>
   <si>
+    <t>Cultural Heritage Protection Plan (if applicable)</t>
+  </si>
+  <si>
     <t>Archaeological Assessment Reports /Permits (provide if they have had them)</t>
   </si>
   <si>
@@ -320,6 +354,9 @@
     <t>Blasting Procedure</t>
   </si>
   <si>
+    <t>Blaster Certificate</t>
+  </si>
+  <si>
     <t>Explosives Magazine Storage and Use Permit (if required)</t>
   </si>
   <si>
@@ -332,13 +369,16 @@
     <t>Appropriate Tenure for qty of material removal (claim/lease amounts)</t>
   </si>
   <si>
+    <t>Mapping - Cross &amp; Long Sections</t>
+  </si>
+  <si>
     <t>ML/ARD</t>
   </si>
   <si>
     <t>Handling Plans</t>
   </si>
   <si>
-    <t>Mill Letter (Inspector Requiest)</t>
+    <t>Mill Letter (Inspector Request)</t>
   </si>
   <si>
     <t>Settling Ponds</t>
@@ -362,7 +402,19 @@
     <t>Other Contacts</t>
   </si>
   <si>
-    <t>Mine Manager Authorization Letter</t>
+    <t>Mine Manager</t>
+  </si>
+  <si>
+    <t>Mine Manager Authorization Letter (if applicable)</t>
+  </si>
+  <si>
+    <t>Permittee</t>
+  </si>
+  <si>
+    <t>Tenure Holder</t>
+  </si>
+  <si>
+    <t>Site Operator</t>
   </si>
   <si>
     <t>MX Tier Category</t>
@@ -395,12 +447,15 @@
     <t>≤ 25 small (15m x 15m) drill sites</t>
   </si>
   <si>
-    <t>&lt; 1km new exploration access construction -No new QP engineered stream crossings</t>
+    <t>&lt; 1km new exploration access construction</t>
   </si>
   <si>
     <t>≤ 5 km existing access modification</t>
   </si>
   <si>
+    <t>No new QP engineered stream crossings</t>
+  </si>
+  <si>
     <t>Seasonal camps including constructed pads</t>
   </si>
   <si>
@@ -440,7 +495,7 @@
     <t>Tier 2 - Activity Level &amp; Land Disturbance</t>
   </si>
   <si>
-    <t>Up to 50 small (20m x20m) unreclaimed at any given time</t>
+    <t>Up to 25 small (20m x20m) unreclaimed at any given time</t>
   </si>
   <si>
     <t>≤ 5 km new exploration access construction</t>
@@ -521,20 +576,600 @@
     <t>Tier 3 - First Nations Consideration</t>
   </si>
   <si>
-    <t>FN engagement has not commenced</t>
-  </si>
-  <si>
     <t>FN has shown opposition to the project</t>
   </si>
   <si>
-    <t>Project area overlaps 5 or more FN (including Bands and other representative bodies)</t>
+    <t>Project area is complex with respect to overlapping First Nation Territories</t>
+  </si>
+  <si>
+    <t>Prompt:</t>
+  </si>
+  <si>
+    <t>You are auditing an application document against this checklist.
+Rules: 
+- Use the checklist from Row 26, down
+- Do not change the conditional formatting. 
+- Mark 'True' if present.
+- Mark 'False' if missing.
+- Mark N/A if it is not applicable.
+- Present means it is a completed section in the form, and/or an attachment is included and listed in the attachment summary section.
+- If unclear, mark 'False'.
+Summary Rules:
+- One sentence summary of the item with wording consistent with the application in column D
+- Provide the applicable page number and do not guess.
+Output format (STRICT):
+- Do not add any extra text.
+- Return only the checklist on the worksheet provided.
+- Ensure all checklist items are included.
+- Ensure formatting matches exactly.
+Determine the tier level based on the activities and information provided in the application. Do not evaluate rows 197 to 199.
+Ignore Rows 29 and 32
+List tenure numbers in D57</t>
+  </si>
+  <si>
+    <t>MX Tiered Intake - April 1, 2026</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>This document explains how to use a shared prompt template with Copilot to support an initial audit of a Notice of Work application against the MX Intake Checklist.</t>
+  </si>
+  <si>
+    <t>This document will evolve as we learn what works well and where adjustments are needed.</t>
+  </si>
+  <si>
+    <t>Outputs must always be reviewed, verified, and interpreted by an analyst before being relied on or shared.</t>
+  </si>
+  <si>
+    <t>Copilot is intended to support analyst review, not replace professional judgement.</t>
+  </si>
+  <si>
+    <t>What Copilot can help with</t>
+  </si>
+  <si>
+    <t>Systematically check whether specific checklist items appear in the application materials provided.</t>
+  </si>
+  <si>
+    <t>Save time on initial completeness and consistency checks.</t>
+  </si>
+  <si>
+    <t>Highlight potential gaps that warrant closer review.</t>
+  </si>
+  <si>
+    <t>What Copilot cannot do</t>
+  </si>
+  <si>
+    <t>Make regulatory decisions or determinations.</t>
+  </si>
+  <si>
+    <t>Inerpret intent, adequacy, or quality beyond what is explicitly present in the text.</t>
+  </si>
+  <si>
+    <t>Replace required technical, Indigenous engagement, or professional judgement reviews.</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IMPORTANT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Copilot may miss information, misinterpret context, or return inconsistent results. Treat outputs as draft working notes, not conclusions.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Open the MX Intake Checklist and 'save as' under the mine file.</t>
+  </si>
+  <si>
+    <t>5. It usually returns the checklist within 5 minutes.</t>
+  </si>
+  <si>
+    <t>4. Copy and paste the prompt template in the text box of the Copilot pane and then click 'send'.</t>
+  </si>
+  <si>
+    <t>3. Click the '+' and upload your Notice of Work.</t>
+  </si>
+  <si>
+    <t>2. Click the Edit with Copilot button.</t>
+  </si>
+  <si>
+    <t>6. Review as appropriate - Do not rely on Copilot output alone.</t>
+  </si>
+  <si>
+    <t>Trouble Shooting</t>
+  </si>
+  <si>
+    <t>Contact Bradley Gretchev or Kristy Rosger</t>
+  </si>
+  <si>
+    <t>FN engagement has not commenced with all applicable First Nations</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,13 +1229,60 @@
       <charset val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -649,8 +1331,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -658,14 +1352,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -673,7 +1384,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
       <extLst>
@@ -688,43 +1401,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
@@ -733,71 +1443,56 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="2"/>
+      <alignment horizontal="left" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <b/>
@@ -920,7 +1615,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BA"/>
@@ -1383,7 +2077,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Rosger, Kristy MCM:EX" id="{D5B29576-CF1B-4310-8120-C302DA5B89E4}" userId="S::Kristy.Rosger@gov.bc.ca::b80b3ede-15ae-4da5-a9f2-d099509b6684" providerId="AD"/>
+  <person displayName="Rosger, Kristy MCM:EX" id="{3AD66213-7952-4151-A2AB-EFD2D96CC873}" userId="S::Kristy.Rosger@gov.bc.ca::b80b3ede-15ae-4da5-a9f2-d099509b6684" providerId="AD"/>
 </personList>
 </file>
 
@@ -1684,1877 +2378,2473 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C142" dT="2026-01-15T18:00:28.66" personId="{D5B29576-CF1B-4310-8120-C302DA5B89E4}" id="{202AD996-6DC7-4D61-8C96-0F781393163C}">
+  <threadedComment ref="C157" dT="2026-01-15T18:00:28.66" personId="{3AD66213-7952-4151-A2AB-EFD2D96CC873}" id="{A6ACB50C-203F-45F9-8AD5-76597DDFFB39}">
     <text>*Based on information provided by the proponent, and verification by MCM</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F998A4A4-050C-4886-A595-1B6A37BC1E66}">
-  <dimension ref="A1:M196"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180AD88D-8E0F-4AAC-87DC-C6AB8A2B1E2F}">
+  <dimension ref="A1:M210"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.21875" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
+    <col min="1" max="2" width="7.28515625" customWidth="1"/>
     <col min="3" max="3" width="79" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="74.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.88671875" customWidth="1"/>
+    <col min="4" max="4" width="74.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="74.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5"/>
     </row>
-    <row r="5" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="45"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="46"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="12"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="12"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="13"/>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="13"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="13"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="14"/>
-      <c r="E21"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="16"/>
       <c r="E26"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="13"/>
-      <c r="D27" s="17"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="14"/>
       <c r="E27"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20"/>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="14"/>
       <c r="E28"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C29" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="17"/>
+      <c r="C29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="14"/>
       <c r="E29"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="17"/>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="14"/>
       <c r="E30"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="17"/>
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="15"/>
       <c r="E31"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="17"/>
+      <c r="C32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="15"/>
       <c r="E32"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="17"/>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="12"/>
+      <c r="D33" s="16"/>
       <c r="E33"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="17"/>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="19"/>
       <c r="E34"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="17"/>
+      <c r="C35" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="16"/>
       <c r="E35"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="22"/>
+      <c r="C36" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="16"/>
       <c r="E36"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C37" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="17"/>
+      <c r="C37" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="16"/>
       <c r="E37"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C38" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" s="17"/>
+      <c r="C38" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="16"/>
       <c r="E38"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="13"/>
-      <c r="D39" s="17"/>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="16"/>
       <c r="E39"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="13"/>
-      <c r="D40" s="17"/>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="16"/>
       <c r="E40"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="18"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="24"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="10"/>
+      <c r="C42" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="21"/>
       <c r="E42"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="10"/>
+      <c r="C43" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="21"/>
       <c r="E43"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="25"/>
+      <c r="C44" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="16"/>
       <c r="E44"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="25"/>
+      <c r="C45" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="16"/>
       <c r="E45"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B46" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="10"/>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="12"/>
+      <c r="D46" s="16"/>
       <c r="E46"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="10"/>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="12"/>
+      <c r="D47" s="16"/>
       <c r="E47"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B48" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="10"/>
-      <c r="E48"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="18"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="23"/>
+    </row>
+    <row r="49" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="10"/>
+      <c r="C49" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="21"/>
       <c r="E49"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C50" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" s="10"/>
+      <c r="C50" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="21"/>
       <c r="E50"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C51" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D51" s="17"/>
+      <c r="C51" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="25"/>
       <c r="E51"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="10"/>
-      <c r="E52"/>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C52" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="25"/>
+      <c r="E52" s="44"/>
+    </row>
+    <row r="53" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D53" s="10"/>
-      <c r="E53"/>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C53" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" s="21"/>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" s="10"/>
-      <c r="E54"/>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C54" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="21"/>
+      <c r="E54" s="44"/>
+    </row>
+    <row r="55" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B55" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="10"/>
+      <c r="C55" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D55" s="21"/>
       <c r="E55"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" s="10"/>
+      <c r="C56" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="21"/>
       <c r="E56"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="10"/>
+      <c r="C57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" s="21"/>
       <c r="E57"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" s="10"/>
+      <c r="C58" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="21"/>
       <c r="E58"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B59" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59" s="10"/>
+      <c r="C59" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="16"/>
       <c r="E59"/>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D60" s="10"/>
+      <c r="C60" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="21"/>
       <c r="E60"/>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" s="10"/>
+      <c r="C61" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="21"/>
       <c r="E61"/>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B62" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="10"/>
+      <c r="C62" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="21"/>
       <c r="E62"/>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B63" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C63" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D63" s="10"/>
+      <c r="C63" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="21"/>
       <c r="E63"/>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B64" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D64" s="10"/>
+      <c r="C64" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D64" s="21"/>
       <c r="E64"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C65" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D65" s="17"/>
+      <c r="C65" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="21"/>
       <c r="E65"/>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C66" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="17"/>
+      <c r="C66" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="21"/>
       <c r="E66"/>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B67" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C67" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D67" s="10"/>
+      <c r="C67" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="21"/>
       <c r="E67"/>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B68" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C68" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D68" s="10"/>
+      <c r="C68" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D68" s="21"/>
       <c r="E68"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B69" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C69" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D69" s="10"/>
+      <c r="C69" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" s="21"/>
       <c r="E69"/>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B70" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C70" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D70" s="10"/>
+      <c r="C70" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="21"/>
       <c r="E70"/>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D71" s="10"/>
+        <v>65</v>
+      </c>
+      <c r="D71" s="21"/>
       <c r="E71"/>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B72" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C72" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D72" s="10"/>
+      <c r="C72" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D72" s="21"/>
       <c r="E72"/>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C73" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D73" s="10"/>
+      <c r="C73" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" s="16"/>
       <c r="E73"/>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B74" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D74" s="10"/>
+      <c r="C74" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" s="16"/>
       <c r="E74"/>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B75" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C75" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="10"/>
+      <c r="C75" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" s="21"/>
       <c r="E75"/>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C76" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D76" s="10"/>
+      <c r="C76" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="21"/>
       <c r="E76"/>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B77" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C77" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D77" s="10"/>
+      <c r="C77" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D77" s="21"/>
       <c r="E77"/>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B78" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D78" s="10"/>
+      <c r="C78" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78" s="21"/>
       <c r="E78"/>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D79" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="D79" s="21"/>
       <c r="E79"/>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B80" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C80" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D80" s="10"/>
+      <c r="C80" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D80" s="21"/>
       <c r="E80"/>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B81" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="C81" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D81" s="10"/>
+    <row r="81" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D81" s="21"/>
       <c r="E81"/>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D82" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="D82" s="21"/>
       <c r="E82"/>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C83" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D83" s="10"/>
+      <c r="C83" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D83" s="21"/>
       <c r="E83"/>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B84" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C84" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D84" s="10"/>
+      <c r="C84" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D84" s="21"/>
       <c r="E84"/>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B85" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C85" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D85" s="10"/>
+      <c r="C85" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D85" s="21"/>
       <c r="E85"/>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B86" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C86" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D86" s="10"/>
+      <c r="C86" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86" s="21"/>
       <c r="E86"/>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C87" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D87" s="10"/>
+      <c r="C87" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D87" s="21"/>
       <c r="E87"/>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B88" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D88" s="10"/>
+      <c r="C88" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" s="21"/>
       <c r="E88"/>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D89" s="10"/>
-      <c r="E89" s="13"/>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C89" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D89" s="21"/>
+      <c r="E89"/>
+    </row>
+    <row r="90" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D90" s="10"/>
-      <c r="E90" s="13"/>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+      <c r="D90" s="21"/>
+      <c r="E90"/>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C91" s="27" t="s">
+      <c r="C91" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D91" s="21"/>
+      <c r="E91"/>
+    </row>
+    <row r="92" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C92" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" s="21"/>
+      <c r="E92"/>
+    </row>
+    <row r="93" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C93" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="D91" s="10"/>
-      <c r="E91" s="13"/>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B92" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C92" s="26" t="s">
+      <c r="D93" s="21"/>
+      <c r="E93"/>
+    </row>
+    <row r="94" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C94" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D94" s="21"/>
+      <c r="E94"/>
+    </row>
+    <row r="95" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C95" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D95" s="21"/>
+      <c r="E95"/>
+    </row>
+    <row r="96" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D96" s="21"/>
+      <c r="E96"/>
+    </row>
+    <row r="97" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D97" s="21"/>
+      <c r="E97" s="12"/>
+    </row>
+    <row r="98" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C98" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D92" s="10"/>
-      <c r="E92" s="13"/>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B93" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C93" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D93" s="10"/>
-      <c r="E93" s="13"/>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B94" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D94" s="10"/>
-      <c r="E94"/>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B95" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D95" s="10"/>
-      <c r="E95" s="13"/>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B96" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C96" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D96" s="10"/>
-      <c r="E96"/>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B97" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C97" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D97" s="10"/>
-      <c r="E97"/>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B98" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C98" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D98" s="10"/>
-      <c r="E98"/>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D98" s="21"/>
+      <c r="E98" s="12"/>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C99" s="27" t="s">
+      <c r="C99" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D99" s="21"/>
+      <c r="E99" s="12"/>
+    </row>
+    <row r="100" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D100" s="21"/>
+      <c r="E100" s="12"/>
+    </row>
+    <row r="101" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C101" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D101" s="21"/>
+      <c r="E101" s="12"/>
+    </row>
+    <row r="102" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D102" s="21"/>
+      <c r="E102"/>
+    </row>
+    <row r="103" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D103" s="21"/>
+      <c r="E103" s="12"/>
+    </row>
+    <row r="104" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B104" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D104" s="21"/>
+      <c r="E104"/>
+    </row>
+    <row r="105" spans="2:5" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C105" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D99" s="10"/>
-      <c r="E99"/>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B100" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C100" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D100" s="10"/>
-      <c r="E100"/>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B101" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C101" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D101" s="10"/>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B102" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C102" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D102" s="10"/>
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B103" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C103" s="11" t="s">
+      <c r="D105" s="21"/>
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C106" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D106" s="21"/>
+      <c r="E106"/>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B107" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D107" s="21"/>
+      <c r="E107"/>
+    </row>
+    <row r="108" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C108" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D108" s="21"/>
+      <c r="E108"/>
+    </row>
+    <row r="109" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C109" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D109" s="21"/>
+      <c r="E109" s="24"/>
+    </row>
+    <row r="110" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C110" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D110" s="21"/>
+      <c r="E110" s="24"/>
+    </row>
+    <row r="111" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D111" s="21"/>
+      <c r="E111" s="24"/>
+    </row>
+    <row r="112" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D112" s="21"/>
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C113" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D113" s="21"/>
+      <c r="E113"/>
+    </row>
+    <row r="114" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C114" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D103" s="10"/>
-      <c r="E103"/>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B104" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C104" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D104" s="10"/>
-      <c r="E104"/>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B105" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="C105" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D105" s="10"/>
-      <c r="E105"/>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B106" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="C106" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D106" s="10"/>
-      <c r="E106"/>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B107" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D107" s="10"/>
-      <c r="E107"/>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B108" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D108" s="10"/>
-      <c r="E108"/>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B109" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C109" s="26" t="s">
+      <c r="D114" s="21"/>
+      <c r="E114"/>
+    </row>
+    <row r="115" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D115" s="21"/>
+      <c r="E115"/>
+    </row>
+    <row r="116" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D116" s="21"/>
+      <c r="E116"/>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B117" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D117" s="21"/>
+      <c r="E117"/>
+    </row>
+    <row r="118" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C118" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D118" s="21"/>
+      <c r="E118"/>
+    </row>
+    <row r="119" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D119" s="21"/>
+      <c r="E119"/>
+    </row>
+    <row r="120" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C120" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D120" s="21"/>
+      <c r="E120"/>
+    </row>
+    <row r="121" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C121" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D121" s="21"/>
+      <c r="E121"/>
+    </row>
+    <row r="122" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D122" s="21"/>
+      <c r="E122"/>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B123" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C123" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D123" s="21"/>
+      <c r="E123"/>
+    </row>
+    <row r="124" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D124" s="21"/>
+      <c r="E124"/>
+    </row>
+    <row r="125" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C125" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D125" s="21"/>
+      <c r="E125"/>
+    </row>
+    <row r="126" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C126" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D109" s="10"/>
-      <c r="E109"/>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B110" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C110" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D110" s="10"/>
-      <c r="E110"/>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B111" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C111" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D111" s="10"/>
-      <c r="E111"/>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B112" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D112" s="10"/>
-      <c r="E112"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B113" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C113" s="2" t="s">
+      <c r="D126" s="21"/>
+      <c r="E126"/>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B127" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C127" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D127" s="21"/>
+      <c r="E127"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B128" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D128" s="21"/>
+      <c r="E128"/>
+    </row>
+    <row r="129" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B129" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C129" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129" s="21"/>
+      <c r="E129"/>
+    </row>
+    <row r="130" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B130" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C130" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D130" s="21"/>
+      <c r="E130"/>
+    </row>
+    <row r="131" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B131" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C131" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D131" s="21"/>
+      <c r="E131"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B132" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C132" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D132" s="21"/>
+      <c r="E132"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B133" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D133" s="21"/>
+      <c r="E133"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B134" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C134" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D134" s="21"/>
+      <c r="E134"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B135" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D135" s="21"/>
+      <c r="E135"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B136" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D136" s="21"/>
+      <c r="E136"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B137" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D137" s="21"/>
+      <c r="E137"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B138" s="12"/>
+      <c r="C138" s="24"/>
+      <c r="D138" s="21"/>
+      <c r="E138"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C139" s="24"/>
+      <c r="D139" s="21"/>
+      <c r="E139"/>
+    </row>
+    <row r="140" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A140" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E140"/>
+    </row>
+    <row r="141" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B141" s="31"/>
+      <c r="C141" s="31"/>
+      <c r="D141" s="32"/>
+      <c r="E141"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B142" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C142" s="18"/>
+      <c r="D142" s="19"/>
+      <c r="E142"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B143" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C143" t="s">
+        <v>118</v>
+      </c>
+      <c r="D143" s="16"/>
+      <c r="E143"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B144" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C144" t="s">
+        <v>119</v>
+      </c>
+      <c r="D144" s="21"/>
+      <c r="E144"/>
+      <c r="M144" s="33"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B145" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C145" t="s">
+        <v>120</v>
+      </c>
+      <c r="D145" s="34"/>
+      <c r="E145"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B146" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>121</v>
+      </c>
+      <c r="D146" s="34"/>
+      <c r="E146"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>122</v>
+      </c>
+      <c r="D147" s="34"/>
+      <c r="E147"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
         <v>89</v>
       </c>
-      <c r="D113" s="10"/>
-      <c r="E113"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B114" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C114" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D114" s="10"/>
-      <c r="E114"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B115" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C115" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D115" s="10"/>
-      <c r="E115"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B116" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D116" s="10"/>
-      <c r="E116"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B117" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C117" s="2" t="s">
+      <c r="D148" s="34"/>
+      <c r="E148"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C149" s="18"/>
+      <c r="D149" s="19"/>
+      <c r="E149"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>124</v>
+      </c>
+      <c r="D150" s="34"/>
+      <c r="E150"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C151" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D151" s="34"/>
+      <c r="E151"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B152" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C152" t="s">
+        <v>126</v>
+      </c>
+      <c r="D152" s="34"/>
+      <c r="E152"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B153" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C153" t="s">
+        <v>127</v>
+      </c>
+      <c r="D153" s="34"/>
+      <c r="E153"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B154" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C154" t="s">
+        <v>128</v>
+      </c>
+      <c r="D154" s="34"/>
+      <c r="E154"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B155" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>129</v>
+      </c>
+      <c r="D155" s="34"/>
+      <c r="E155"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B156" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C156" s="18"/>
+      <c r="D156" s="19"/>
+      <c r="E156"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B157" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>131</v>
+      </c>
+      <c r="D157" s="34"/>
+      <c r="E157"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B158" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>132</v>
+      </c>
+      <c r="D158" s="34"/>
+      <c r="E158"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B159" s="12"/>
+      <c r="D159" s="34"/>
+      <c r="E159"/>
+    </row>
+    <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B160" s="31"/>
+      <c r="C160" s="31"/>
+      <c r="D160" s="32"/>
+      <c r="E160"/>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B161" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C161" s="18"/>
+      <c r="D161" s="19"/>
+      <c r="E161"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B162" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C162" t="s">
+        <v>135</v>
+      </c>
+      <c r="D162" s="34"/>
+      <c r="E162"/>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B163" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C163" t="s">
+        <v>136</v>
+      </c>
+      <c r="D163" s="34"/>
+      <c r="E163"/>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B164" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>137</v>
+      </c>
+      <c r="D164" s="34"/>
+      <c r="E164"/>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B165" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s">
+        <v>138</v>
+      </c>
+      <c r="D165" s="34"/>
+      <c r="E165"/>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B166" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C166" t="s">
+        <v>139</v>
+      </c>
+      <c r="D166" s="34"/>
+      <c r="E166"/>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B167" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C167" s="18"/>
+      <c r="D167" s="19"/>
+      <c r="E167"/>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B168" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D168" s="34"/>
+      <c r="E168"/>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B169" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D169" s="34"/>
+      <c r="E169"/>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B170" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D170" s="34"/>
+      <c r="E170"/>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B171" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>144</v>
+      </c>
+      <c r="D171" s="34"/>
+      <c r="E171"/>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B172" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>145</v>
+      </c>
+      <c r="D172" s="34"/>
+      <c r="E172"/>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B173" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C173" t="s">
+        <v>146</v>
+      </c>
+      <c r="D173" s="34"/>
+      <c r="E173"/>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B174" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C174" s="18"/>
+      <c r="D174" s="19"/>
+      <c r="E174"/>
+    </row>
+    <row r="175" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B175" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C175" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="D175" s="34"/>
+      <c r="E175"/>
+    </row>
+    <row r="176" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B176" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C176" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="D176" s="34"/>
+      <c r="E176"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B177" s="12"/>
+      <c r="C177" s="37"/>
+      <c r="D177" s="34"/>
+      <c r="E177"/>
+    </row>
+    <row r="178" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A178" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B178" s="31"/>
+      <c r="C178" s="31"/>
+      <c r="D178" s="32"/>
+      <c r="E178"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B179" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C179" s="18"/>
+      <c r="D179" s="19"/>
+      <c r="E179"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B180" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
         <v>90</v>
       </c>
-      <c r="D117" s="29"/>
-      <c r="E117"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B118" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D118" s="10"/>
-      <c r="E118"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B119" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C119" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D119" s="10"/>
-      <c r="E119"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B120" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D120" s="10"/>
-      <c r="E120"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B121" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D121" s="10"/>
-      <c r="E121"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B122" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D122" s="10"/>
-      <c r="E122"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B123" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D123" s="10"/>
-      <c r="E123"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B124" s="13"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="10"/>
-      <c r="E124"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C125" s="2"/>
-      <c r="D125" s="10"/>
-      <c r="E125"/>
-    </row>
-    <row r="126" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A126" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="14"/>
-      <c r="E126"/>
-    </row>
-    <row r="127" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A127" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B127" s="31"/>
-      <c r="C127" s="31"/>
-      <c r="D127" s="32"/>
-      <c r="E127"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B128" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C128" s="19"/>
-      <c r="D128" s="20"/>
-      <c r="E128"/>
-    </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B129" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C129" t="s">
-        <v>100</v>
-      </c>
-      <c r="D129" s="17"/>
-      <c r="E129"/>
-    </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B130" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C130" t="s">
-        <v>101</v>
-      </c>
-      <c r="D130" s="10"/>
-      <c r="E130"/>
-      <c r="M130" s="33"/>
-    </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B131" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C131" t="s">
-        <v>102</v>
-      </c>
-      <c r="D131" s="3"/>
-      <c r="E131"/>
-    </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B132" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C132" t="s">
-        <v>103</v>
-      </c>
-      <c r="D132" s="3"/>
-      <c r="E132"/>
-    </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B133" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C133" t="s">
-        <v>104</v>
-      </c>
-      <c r="D133" s="3"/>
-      <c r="E133"/>
-    </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B134" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C134" t="s">
-        <v>77</v>
-      </c>
-      <c r="D134" s="3"/>
-      <c r="E134"/>
-    </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B135" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C135" s="19"/>
-      <c r="D135" s="20"/>
-      <c r="E135"/>
-    </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B136" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C136" t="s">
-        <v>106</v>
-      </c>
-      <c r="D136" s="3"/>
-      <c r="E136"/>
-    </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B137" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C137" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D137" s="3"/>
-      <c r="E137"/>
-    </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B138" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C138" t="s">
-        <v>108</v>
-      </c>
-      <c r="D138" s="3"/>
-      <c r="E138"/>
-    </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B139" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C139" t="s">
-        <v>109</v>
-      </c>
-      <c r="D139" s="3"/>
-      <c r="E139"/>
-    </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B140" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C140" t="s">
-        <v>110</v>
-      </c>
-      <c r="D140" s="3"/>
-      <c r="E140"/>
-    </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B141" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C141" s="19"/>
-      <c r="D141" s="20"/>
-      <c r="E141"/>
-    </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B142" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C142" t="s">
-        <v>112</v>
-      </c>
-      <c r="D142" s="3"/>
-      <c r="E142"/>
-    </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B143" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C143" t="s">
-        <v>113</v>
-      </c>
-      <c r="D143" s="3"/>
-      <c r="E143"/>
-    </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B144" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D144" s="3"/>
-      <c r="E144"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B145" s="13"/>
-      <c r="D145" s="3"/>
-      <c r="E145"/>
-    </row>
-    <row r="146" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A146" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="B146" s="31"/>
-      <c r="C146" s="31"/>
-      <c r="D146" s="32"/>
-      <c r="E146"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B147" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C147" s="19"/>
-      <c r="D147" s="20"/>
-      <c r="E147"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B148" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C148" t="s">
-        <v>116</v>
-      </c>
-      <c r="D148" s="3"/>
-      <c r="E148"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B149" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C149" t="s">
-        <v>117</v>
-      </c>
-      <c r="D149" s="3"/>
-      <c r="E149"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B150" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C150" t="s">
-        <v>118</v>
-      </c>
-      <c r="D150" s="3"/>
-      <c r="E150"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B151" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C151" t="s">
-        <v>119</v>
-      </c>
-      <c r="D151" s="3"/>
-      <c r="E151"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B152" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C152" t="s">
-        <v>120</v>
-      </c>
-      <c r="D152" s="3"/>
-      <c r="E152"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B153" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C153" s="19"/>
-      <c r="D153" s="20"/>
-      <c r="E153"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B154" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C154" t="s">
-        <v>122</v>
-      </c>
-      <c r="D154" s="3"/>
-      <c r="E154"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B155" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C155" t="s">
-        <v>123</v>
-      </c>
-      <c r="D155" s="3"/>
-      <c r="E155"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B156" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C156" t="s">
-        <v>124</v>
-      </c>
-      <c r="D156" s="3"/>
-      <c r="E156"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B157" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C157" t="s">
-        <v>125</v>
-      </c>
-      <c r="D157" s="3"/>
-      <c r="E157"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B158" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C158" t="s">
-        <v>126</v>
-      </c>
-      <c r="D158" s="3"/>
-      <c r="E158"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B159" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C159" t="s">
-        <v>127</v>
-      </c>
-      <c r="D159" s="3"/>
-      <c r="E159"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B160" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C160" s="19"/>
-      <c r="D160" s="20"/>
-      <c r="E160"/>
-    </row>
-    <row r="161" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B161" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C161" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D161" s="3"/>
-      <c r="E161"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B162" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C162" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="D162" s="3"/>
-      <c r="E162"/>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B163" s="13"/>
-      <c r="C163" s="22"/>
-      <c r="D163" s="3"/>
-      <c r="E163"/>
-    </row>
-    <row r="164" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A164" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="B164" s="31"/>
-      <c r="C164" s="31"/>
-      <c r="D164" s="32"/>
-      <c r="E164"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B165" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="C165" s="19"/>
-      <c r="D165" s="20"/>
-      <c r="E165"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B166" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C166" t="s">
-        <v>78</v>
-      </c>
-      <c r="D166" s="3"/>
-      <c r="E166"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B167" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C167" t="s">
-        <v>133</v>
-      </c>
-      <c r="D167" s="3"/>
-      <c r="E167"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B168" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C168" t="s">
-        <v>134</v>
-      </c>
-      <c r="D168" s="3"/>
-      <c r="E168"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B169" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C169" t="s">
-        <v>135</v>
-      </c>
-      <c r="D169" s="3"/>
-      <c r="E169"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B170" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C170" t="s">
-        <v>136</v>
-      </c>
-      <c r="D170" s="3"/>
-      <c r="E170"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B171" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C171" t="s">
-        <v>137</v>
-      </c>
-      <c r="D171" s="3"/>
-      <c r="E171"/>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B172" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C172" t="s">
-        <v>138</v>
-      </c>
-      <c r="D172" s="3"/>
-      <c r="E172"/>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B173" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C173" t="s">
-        <v>139</v>
-      </c>
-      <c r="D173" s="3"/>
-      <c r="E173"/>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B174" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C174" s="19"/>
-      <c r="D174" s="20"/>
-      <c r="E174"/>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B175" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C175" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="D175" s="3"/>
-      <c r="E175"/>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B176" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C176" t="s">
-        <v>142</v>
-      </c>
-      <c r="D176" s="3"/>
-      <c r="E176"/>
-    </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B177" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C177" t="s">
-        <v>143</v>
-      </c>
-      <c r="D177" s="3"/>
-      <c r="E177"/>
-    </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B178" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C178" t="s">
-        <v>144</v>
-      </c>
-      <c r="D178" s="3"/>
-      <c r="E178"/>
-    </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B179" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C179" t="s">
-        <v>145</v>
-      </c>
-      <c r="D179" s="3"/>
-      <c r="E179"/>
-    </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B180" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C180" t="s">
-        <v>146</v>
-      </c>
-      <c r="D180" s="3"/>
+      <c r="D180" s="34"/>
       <c r="E180"/>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B181" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>147</v>
-      </c>
-      <c r="D181" s="3"/>
+        <v>152</v>
+      </c>
+      <c r="D181" s="34"/>
       <c r="E181"/>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B182" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C182" s="19"/>
-      <c r="D182" s="20"/>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B182" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>153</v>
+      </c>
+      <c r="D182" s="34"/>
       <c r="E182"/>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B183" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>149</v>
-      </c>
-      <c r="D183" s="3"/>
+        <v>154</v>
+      </c>
+      <c r="D183" s="34"/>
       <c r="E183"/>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B184" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>150</v>
-      </c>
-      <c r="D184" s="3"/>
+        <v>155</v>
+      </c>
+      <c r="D184" s="34"/>
       <c r="E184"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B185" s="9" t="b">
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>151</v>
-      </c>
-      <c r="D185" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="D185" s="34"/>
       <c r="E185"/>
-      <c r="F185" s="34"/>
-    </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C186" s="2"/>
-      <c r="D186" s="3"/>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B186" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C186" t="s">
+        <v>157</v>
+      </c>
+      <c r="D186" s="34"/>
       <c r="E186"/>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C187" s="2"/>
-      <c r="D187" s="3"/>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B187" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C187" t="s">
+        <v>158</v>
+      </c>
+      <c r="D187" s="34"/>
       <c r="E187"/>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C188" s="2"/>
-      <c r="D188" s="3"/>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B188" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C188" s="18"/>
+      <c r="D188" s="19"/>
       <c r="E188"/>
-      <c r="F188" s="34"/>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C189" s="2"/>
-      <c r="D189" s="3"/>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B189" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C189" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D189" s="34"/>
       <c r="E189"/>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C190" s="2"/>
-      <c r="D190" s="3"/>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B190" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C190" t="s">
+        <v>161</v>
+      </c>
+      <c r="D190" s="34"/>
       <c r="E190"/>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C191" s="2"/>
-      <c r="D191" s="3"/>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B191" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>162</v>
+      </c>
+      <c r="D191" s="34"/>
       <c r="E191"/>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C192" s="2"/>
-      <c r="D192" s="3"/>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B192" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>163</v>
+      </c>
+      <c r="D192" s="34"/>
       <c r="E192"/>
     </row>
-    <row r="193" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C193" s="2"/>
-      <c r="D193" s="3"/>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B193" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>164</v>
+      </c>
+      <c r="D193" s="34"/>
       <c r="E193"/>
     </row>
-    <row r="194" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C194" s="2"/>
-      <c r="D194" s="3"/>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B194" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>165</v>
+      </c>
+      <c r="D194" s="34"/>
       <c r="E194"/>
     </row>
-    <row r="195" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C195" s="2"/>
-      <c r="D195" s="3"/>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B195" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>166</v>
+      </c>
+      <c r="D195" s="34"/>
       <c r="E195"/>
     </row>
-    <row r="196" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C196" s="2"/>
-      <c r="D196" s="3"/>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B196" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C196" s="18"/>
+      <c r="D196" s="19"/>
       <c r="E196"/>
     </row>
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B197" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C197" t="s">
+        <v>196</v>
+      </c>
+      <c r="D197" s="34"/>
+      <c r="E197"/>
+    </row>
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B198" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C198" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="D198" s="34"/>
+      <c r="E198"/>
+    </row>
+    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B199" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C199" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="D199" s="34"/>
+      <c r="E199"/>
+      <c r="F199" s="38"/>
+    </row>
+    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C200" s="24"/>
+      <c r="D200" s="34"/>
+      <c r="E200"/>
+    </row>
+    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C201" s="24"/>
+      <c r="D201" s="34"/>
+      <c r="E201"/>
+    </row>
+    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C202" s="24"/>
+      <c r="D202" s="34"/>
+      <c r="E202"/>
+      <c r="F202" s="38"/>
+    </row>
+    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C203" s="24"/>
+      <c r="D203" s="34"/>
+      <c r="E203"/>
+    </row>
+    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C204" s="24"/>
+      <c r="D204" s="34"/>
+      <c r="E204"/>
+    </row>
+    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C205" s="24"/>
+      <c r="D205" s="34"/>
+      <c r="E205"/>
+    </row>
+    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C206" s="24"/>
+      <c r="D206" s="34"/>
+      <c r="E206"/>
+    </row>
+    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C207" s="24"/>
+      <c r="D207" s="34"/>
+      <c r="E207"/>
+    </row>
+    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C208" s="24"/>
+      <c r="D208" s="34"/>
+      <c r="E208"/>
+    </row>
+    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C209" s="24"/>
+      <c r="D209" s="34"/>
+      <c r="E209"/>
+    </row>
+    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C210" s="24"/>
+      <c r="D210" s="34"/>
+      <c r="E210"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A21">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>AND($A21=FALSE,$A21&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>AND($A26=FALSE,$A26&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A126">
-    <cfRule type="expression" dxfId="9" priority="6">
-      <formula>AND($A126=FALSE,$A126&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="A140">
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>AND($A140=FALSE,$A140&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A127">
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>AND($B127=FALSE,$B127&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="A178">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND($B178=FALSE,$B178&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A146">
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>AND($B146=FALSE,$B146&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A164">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>AND($B164=FALSE,$B164&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:D5">
-    <cfRule type="expression" dxfId="5" priority="8">
+  <conditionalFormatting sqref="A5:D5 C6:C10 C17:C25">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>AND($C5=FALSE,$C5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B124">
-    <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND($B22=FALSE,$B22&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="B6:B23 A141">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>AND($B6=FALSE,$B6&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128:B145">
-    <cfRule type="expression" dxfId="3" priority="7">
-      <formula>AND($B128=FALSE,$B128&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="B27:B138 B142:B159 A160">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>AND($B27=FALSE,$B27&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147:B163">
-    <cfRule type="expression" dxfId="2" priority="5">
-      <formula>AND($B147=FALSE,$B147&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="B161:B177">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>AND($B161=FALSE,$B161&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B165:B185">
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>AND($B165=FALSE,$B165&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C10 C13:C20">
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>AND($C6=FALSE,$C6&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="B179:B199">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>AND($B179=FALSE,$B179&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{068F01D7-5D02-4F95-99C3-63C41D818240}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D29" xr:uid="{65ADEF8E-05C9-4426-8970-F2C0527AE3D3}">
       <formula1>"New: MYAB, New: Site-Specific, Amendment: MYAB, Amendment: Site-Specific"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A32FB11-DF71-4AC2-A068-CB35004E9876}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="38" customWidth="1"/>
+    <col min="2" max="2" width="137.7109375" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="39"/>
+      <c r="B3" s="38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="39"/>
+      <c r="B4" s="38" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="39"/>
+      <c r="B5" s="38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="39"/>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="39"/>
+      <c r="B7" s="42" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="39"/>
+      <c r="B8" s="38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="39"/>
+      <c r="B9" s="38" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="39"/>
+      <c r="B10" s="38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="39"/>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="39"/>
+      <c r="B12" s="42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="39"/>
+      <c r="B13" s="38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="39"/>
+      <c r="B14" s="38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="39"/>
+      <c r="B15" s="38" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="39"/>
+      <c r="B16" s="38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="39"/>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="39"/>
+      <c r="B19" s="38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="39"/>
+      <c r="B20" s="38" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="39"/>
+      <c r="B21" s="38" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="39"/>
+      <c r="B22" s="38" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="39"/>
+      <c r="B23" s="38" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="39"/>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="39"/>
+    </row>
+    <row r="27" spans="1:2" ht="390" x14ac:dyDescent="0.25">
+      <c r="A27" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb379a16-fe9a-4f99-9ebe-90fc04df7cbd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100267A2BFF8797D040A1A18AF89E138D86" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c45862a1c7ff9e0e86cc114832d0538c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eb379a16-fe9a-4f99-9ebe-90fc04df7cbd" xmlns:ns3="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bb06a13253d49b6d9132a0d7c523176b" ns2:_="" ns3:_="">
+    <xsd:import namespace="eb379a16-fe9a-4f99-9ebe-90fc04df7cbd"/>
+    <xsd:import namespace="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="eb379a16-fe9a-4f99-9ebe-90fc04df7cbd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="a9b50559-7390-452f-8d4d-780c6c1e431b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="20" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4941beb4-1110-4c53-bba7-189fff331496}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C894B845-12F0-4CB5-8142-53FCB5745B2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10A36709-C1BE-4B26-9C00-B97E0E038BAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb379a16-fe9a-4f99-9ebe-90fc04df7cbd"/>
+    <ds:schemaRef ds:uri="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD6CA-869A-42FF-A818-F6A1EE81199D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="eb379a16-fe9a-4f99-9ebe-90fc04df7cbd"/>
+    <ds:schemaRef ds:uri="e98aa8a9-5ed1-472a-9a9a-b41dba49bfb0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>